--- a/Dados.xlsx
+++ b/Dados.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\proje\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\miguel.luz\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="12130"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12210"/>
   </bookViews>
   <sheets>
     <sheet name="Página1" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="59">
   <si>
     <t>Medida</t>
   </si>
@@ -178,15 +178,36 @@
   </si>
   <si>
     <t>y</t>
+  </si>
+  <si>
+    <t>Corrente Aplicada[A]</t>
+  </si>
+  <si>
+    <t>Corrente Medida [A]</t>
+  </si>
+  <si>
+    <t>I Medida (A)</t>
+  </si>
+  <si>
+    <t>I Aplicada (A)</t>
+  </si>
+  <si>
+    <t>erro (A)</t>
+  </si>
+  <si>
+    <t>erro (%)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="2">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="0.0000000"/>
     <numFmt numFmtId="165" formatCode="0.00000"/>
+    <numFmt numFmtId="166" formatCode="0.0000"/>
+    <numFmt numFmtId="167" formatCode="0.000"/>
+    <numFmt numFmtId="168" formatCode="0.0"/>
   </numFmts>
   <fonts count="15" x14ac:knownFonts="1">
     <font>
@@ -418,7 +439,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -453,6 +474,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="18">
     <cellStyle name="Accent" xfId="7"/>
@@ -606,11 +639,11 @@
               <a:effectLst/>
             </c:spPr>
             <c:trendlineType val="linear"/>
-            <c:dispRSqr val="1"/>
+            <c:dispRSqr val="0"/>
             <c:dispEq val="1"/>
             <c:trendlineLbl>
               <c:layout/>
-              <c:numFmt formatCode="#,##0.000000" sourceLinked="0"/>
+              <c:numFmt formatCode="#,##0.00000000000" sourceLinked="0"/>
               <c:spPr>
                 <a:noFill/>
                 <a:ln>
@@ -647,97 +680,46 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="31"/>
                 <c:pt idx="0" formatCode="0">
-                  <c:v>166</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>452</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>132</c:v>
+                  <c:v>9</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>342</c:v>
+                  <c:v>67</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>110</c:v>
-                </c:pt>
-                <c:pt idx="5" formatCode="0">
-                  <c:v>277</c:v>
+                  <c:v>128</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>431</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>85</c:v>
+                  <c:v>740</c:v>
                 </c:pt>
                 <c:pt idx="7" formatCode="0">
-                  <c:v>218</c:v>
+                  <c:v>1053</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>73</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>190</c:v>
+                  <c:v>1363</c:v>
+                </c:pt>
+                <c:pt idx="9" formatCode="0">
+                  <c:v>1678</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>57</c:v>
+                  <c:v>1989</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>150</c:v>
+                  <c:v>2305</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>45</c:v>
+                  <c:v>2622</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>125</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>199</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>592</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>519</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>182</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>166</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>456</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>449</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>195</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>582</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>237</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>785</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>678</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>216</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>380</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>555</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>306</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>359</c:v>
+                  <c:v>2945</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -749,97 +731,46 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="31"/>
                 <c:pt idx="0">
-                  <c:v>0.50900000000000001</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.96299999999999997</c:v>
+                  <c:v>0.27</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.45600000000000002</c:v>
+                  <c:v>0.3</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.78900000000000003</c:v>
+                  <c:v>0.4</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.42</c:v>
+                  <c:v>0.5</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.68700000000000006</c:v>
+                  <c:v>0.999</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.38300000000000001</c:v>
+                  <c:v>1.4990000000000001</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.59299999999999997</c:v>
+                  <c:v>1.9970000000000001</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.36399999999999999</c:v>
+                  <c:v>2.4980000000000002</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.54800000000000004</c:v>
+                  <c:v>2.9990000000000001</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.33600000000000002</c:v>
+                  <c:v>3.4990000000000001</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.48599999999999999</c:v>
+                  <c:v>4.0010000000000003</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.316</c:v>
+                  <c:v>4.4989999999999997</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.44600000000000001</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>0.56299999999999994</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>1.1779999999999999</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>1.0649999999999999</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>0.53600000000000003</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>0.51100000000000001</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>0.96899999999999997</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>0.96299999999999997</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>0.56200000000000006</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>1.1719999999999999</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>0.627</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>1.4910000000000001</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>1.3180000000000001</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>0.59399999999999997</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>0.85099999999999998</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>1.119</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>0.73499999999999999</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>0.81899999999999995</c:v>
+                  <c:v>4.9969999999999999</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1031,7 +962,863 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="pt-BR"/>
+              <a:t>I nominal X I medido</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="pt-BR"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>I nominal</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="10"/>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:srgbClr val="FF0000"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Página1!$N$40:$N$50</c:f>
+              <c:numCache>
+                <c:formatCode>0.000</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>0.26800000000000002</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.499</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.0029999999999999</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.502</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.998</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2.5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2.9990000000000001</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>3.4990000000000001</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>4.0039999999999996</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>4.4989999999999997</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>4.9969999999999999</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-D1F3-4151-B5C3-BFD3DFBF12EF}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>I medido</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="x"/>
+            <c:size val="10"/>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:srgbClr val="0070C0"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Página1!$O$40:$O$50</c:f>
+              <c:numCache>
+                <c:formatCode>0.000</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>0.252</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.45700000000000002</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.95499999999999996</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.456</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.9650000000000001</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2.4700000000000002</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2.9830000000000001</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>3.4870000000000001</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>4.0030000000000001</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>4.5110000000000001</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>5.0430000000000001</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-D1F3-4151-B5C3-BFD3DFBF12EF}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="794740816"/>
+        <c:axId val="794729584"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="794740816"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="pt-BR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="794729584"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="794729584"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.000" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="pt-BR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="794740816"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="pt-BR"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="pt-BR"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="pt-BR"/>
+              <a:t>Erro %</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="pt-BR"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.1070255905511811"/>
+          <c:y val="0.19721055701370663"/>
+          <c:w val="0.86364107611548557"/>
+          <c:h val="0.77736111111111106"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="diamond"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:srgbClr val="FF0000"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Página1!$Q$40:$Q$50</c:f>
+              <c:numCache>
+                <c:formatCode>0.0</c:formatCode>
+                <c:ptCount val="11"/>
+                <c:pt idx="0">
+                  <c:v>-5.9701492537313481</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-8.4168336673346644</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-4.7856430707876303</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-3.0625832223701757</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-1.6516516516516477</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-1.1999999999999922</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-0.53351117039013052</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>-0.34295513003715378</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>-2.4975024975011136E-2</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.26672593909758735</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.92055233139884463</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-2C16-45B6-9ABB-DF29E560F327}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="789661680"/>
+        <c:axId val="789664176"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="789661680"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="pt-BR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="789664176"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="789664176"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.0" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="pt-BR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="789661680"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="pt-BR"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -1587,20 +2374,1052 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>46062</xdr:colOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>512787</xdr:colOff>
       <xdr:row>2</xdr:row>
-      <xdr:rowOff>17941</xdr:rowOff>
+      <xdr:rowOff>65566</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>21</xdr:col>
-      <xdr:colOff>60475</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>161268</xdr:rowOff>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>527200</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>27918</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -1614,6 +3433,66 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>1590675</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>171451</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>600075</xdr:colOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>190500</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>33336</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>152399</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>200024</xdr:colOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1885,24 +3764,27 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L49"/>
-  <sheetFormatPr defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:Q54"/>
+  <sheetFormatPr defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="26.75" customWidth="1"/>
-    <col min="2" max="2" width="13.08203125" customWidth="1"/>
+    <col min="2" max="2" width="13.125" customWidth="1"/>
     <col min="3" max="3" width="13.75" customWidth="1"/>
     <col min="4" max="4" width="42.75" customWidth="1"/>
     <col min="5" max="5" width="6.5" customWidth="1"/>
-    <col min="6" max="6" width="24.08203125" customWidth="1"/>
-    <col min="7" max="8" width="11.6640625" customWidth="1"/>
-    <col min="9" max="9" width="14.08203125" customWidth="1"/>
-    <col min="10" max="10" width="14.83203125" customWidth="1"/>
-    <col min="11" max="11" width="18.6640625" customWidth="1"/>
+    <col min="6" max="6" width="24.125" customWidth="1"/>
+    <col min="7" max="8" width="11.625" customWidth="1"/>
+    <col min="9" max="9" width="14.125" customWidth="1"/>
+    <col min="10" max="10" width="14.875" customWidth="1"/>
+    <col min="11" max="11" width="18.625" customWidth="1"/>
     <col min="12" max="12" width="21" customWidth="1"/>
-    <col min="13" max="1024" width="11.6640625" customWidth="1"/>
+    <col min="13" max="13" width="18.75" customWidth="1"/>
+    <col min="14" max="14" width="18" customWidth="1"/>
+    <col min="15" max="15" width="16" customWidth="1"/>
+    <col min="16" max="1024" width="11.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1933,7 +3815,7 @@
       <c r="J1" s="2"/>
       <c r="K1" s="2"/>
     </row>
-    <row r="2" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>9</v>
       </c>
@@ -1965,7 +3847,7 @@
       <c r="J2" s="2"/>
       <c r="K2" s="2"/>
     </row>
-    <row r="3" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
         <v>12</v>
       </c>
@@ -1997,7 +3879,7 @@
       <c r="J3" s="2"/>
       <c r="K3" s="2"/>
     </row>
-    <row r="4" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
         <v>16</v>
       </c>
@@ -2029,7 +3911,7 @@
       <c r="J4" s="2"/>
       <c r="K4" s="2"/>
     </row>
-    <row r="5" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
         <v>19</v>
       </c>
@@ -2061,7 +3943,7 @@
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
     </row>
-    <row r="6" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
         <v>22</v>
       </c>
@@ -2091,7 +3973,7 @@
       <c r="J6" s="2"/>
       <c r="K6" s="2"/>
     </row>
-    <row r="7" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
         <v>24</v>
       </c>
@@ -2121,7 +4003,7 @@
       <c r="J7" s="2"/>
       <c r="K7" s="2"/>
     </row>
-    <row r="8" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
         <v>26</v>
       </c>
@@ -2151,7 +4033,7 @@
       <c r="J8" s="2"/>
       <c r="K8" s="2"/>
     </row>
-    <row r="9" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
         <v>27</v>
       </c>
@@ -2168,7 +4050,7 @@
       <c r="J9" s="2"/>
       <c r="K9" s="2"/>
     </row>
-    <row r="10" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>28</v>
       </c>
@@ -2188,7 +4070,7 @@
       <c r="J10" s="2"/>
       <c r="K10" s="2"/>
     </row>
-    <row r="11" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
         <v>32</v>
       </c>
@@ -2208,7 +4090,7 @@
       <c r="J11" s="2"/>
       <c r="K11" s="2"/>
     </row>
-    <row r="12" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
         <v>34</v>
       </c>
@@ -2228,7 +4110,7 @@
       <c r="J12" s="2"/>
       <c r="K12" s="2"/>
     </row>
-    <row r="13" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
         <v>34</v>
       </c>
@@ -2248,7 +4130,7 @@
       <c r="J13" s="2"/>
       <c r="K13" s="2"/>
     </row>
-    <row r="14" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
         <v>36</v>
       </c>
@@ -2268,7 +4150,7 @@
       <c r="J14" s="2"/>
       <c r="K14" s="2"/>
     </row>
-    <row r="15" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
@@ -2279,14 +4161,14 @@
       <c r="I15" s="5"/>
       <c r="K15" s="2"/>
     </row>
-    <row r="16" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
       <c r="D16" s="2"/>
       <c r="K16" s="2"/>
     </row>
-    <row r="17" spans="1:12" ht="14" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:13" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A17" s="6" t="s">
         <v>37</v>
       </c>
@@ -2296,10 +4178,13 @@
         <v>8</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" ht="14" x14ac:dyDescent="0.3">
+        <v>53</v>
+      </c>
+      <c r="M17" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
         <v>38</v>
       </c>
@@ -2334,7 +4219,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="19" spans="1:12" ht="14" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:13" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
         <v>45</v>
       </c>
@@ -2360,13 +4245,13 @@
       <c r="H19" s="3"/>
       <c r="I19" s="3"/>
       <c r="K19" s="5">
-        <v>166</v>
+        <v>0</v>
       </c>
       <c r="L19" s="3">
-        <v>0.50900000000000001</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" ht="14" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
         <v>46</v>
       </c>
@@ -2385,13 +4270,13 @@
       <c r="H20" s="3"/>
       <c r="I20" s="3"/>
       <c r="K20" s="3">
-        <v>452</v>
+        <v>1</v>
       </c>
       <c r="L20" s="3">
-        <v>0.96299999999999997</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" ht="14" x14ac:dyDescent="0.3">
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
         <v>47</v>
       </c>
@@ -2410,13 +4295,13 @@
       <c r="H21" s="3"/>
       <c r="I21" s="3"/>
       <c r="K21" s="3">
-        <v>132</v>
+        <v>9</v>
       </c>
       <c r="L21" s="3">
-        <v>0.45600000000000002</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" ht="14" x14ac:dyDescent="0.3">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
         <v>48</v>
       </c>
@@ -2435,13 +4320,13 @@
       <c r="H22" s="3"/>
       <c r="I22" s="3"/>
       <c r="K22" s="3">
-        <v>342</v>
+        <v>67</v>
       </c>
       <c r="L22" s="3">
-        <v>0.78900000000000003</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" ht="14" x14ac:dyDescent="0.3">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C23" s="2"/>
       <c r="E23" s="2"/>
       <c r="F23" s="3">
@@ -2453,13 +4338,13 @@
       <c r="H23" s="3"/>
       <c r="I23" s="3"/>
       <c r="K23" s="3">
-        <v>110</v>
+        <v>128</v>
       </c>
       <c r="L23" s="3">
-        <v>0.42</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12" ht="14" x14ac:dyDescent="0.3">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" ht="14.25" x14ac:dyDescent="0.2">
       <c r="C24" s="2"/>
       <c r="E24" s="2"/>
       <c r="F24" s="3">
@@ -2470,14 +4355,14 @@
       </c>
       <c r="H24" s="3"/>
       <c r="I24" s="3"/>
-      <c r="K24" s="5">
-        <v>277</v>
+      <c r="K24" s="3">
+        <v>431</v>
       </c>
       <c r="L24" s="3">
-        <v>0.68700000000000006</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12" ht="14" x14ac:dyDescent="0.3">
+        <v>0.999</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
         <v>49</v>
       </c>
@@ -2495,13 +4380,13 @@
       <c r="H25" s="3"/>
       <c r="I25" s="3"/>
       <c r="K25" s="3">
-        <v>85</v>
+        <v>740</v>
       </c>
       <c r="L25" s="3">
-        <v>0.38300000000000001</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12" ht="14" x14ac:dyDescent="0.3">
+        <v>1.4990000000000001</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A26" s="3">
         <f>F19*G19</f>
         <v>84.494</v>
@@ -2520,13 +4405,13 @@
       <c r="H26" s="3"/>
       <c r="I26" s="3"/>
       <c r="K26" s="5">
-        <v>218</v>
+        <v>1053</v>
       </c>
       <c r="L26" s="3">
-        <v>0.59299999999999997</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12" ht="14" x14ac:dyDescent="0.3">
+        <v>1.9970000000000001</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A27" s="3">
         <f>F20*G20</f>
         <v>435.27600000000001</v>
@@ -2544,13 +4429,13 @@
       <c r="H27" s="3"/>
       <c r="I27" s="3"/>
       <c r="K27" s="3">
-        <v>73</v>
+        <v>1363</v>
       </c>
       <c r="L27" s="3">
-        <v>0.36399999999999999</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12" ht="14" x14ac:dyDescent="0.3">
+        <v>2.4980000000000002</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A28" s="3">
         <f t="shared" ref="A28:A34" si="0">F22*G22</f>
         <v>269.83800000000002</v>
@@ -2567,14 +4452,14 @@
       </c>
       <c r="H28" s="3"/>
       <c r="I28" s="3"/>
-      <c r="K28" s="3">
-        <v>190</v>
+      <c r="K28" s="5">
+        <v>1678</v>
       </c>
       <c r="L28" s="3">
-        <v>0.54800000000000004</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12" ht="14" x14ac:dyDescent="0.3">
+        <v>2.9990000000000001</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A29" s="3">
         <f t="shared" si="0"/>
         <v>46.199999999999996</v>
@@ -2592,13 +4477,13 @@
       <c r="H29" s="3"/>
       <c r="I29" s="3"/>
       <c r="K29" s="3">
-        <v>57</v>
+        <v>1989</v>
       </c>
       <c r="L29" s="3">
-        <v>0.33600000000000002</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12" ht="14" x14ac:dyDescent="0.3">
+        <v>3.4990000000000001</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A30" s="3">
         <f t="shared" si="0"/>
         <v>190.29900000000001</v>
@@ -2616,13 +4501,13 @@
       <c r="H30" s="3"/>
       <c r="I30" s="3"/>
       <c r="K30" s="3">
-        <v>150</v>
+        <v>2305</v>
       </c>
       <c r="L30" s="3">
-        <v>0.48599999999999999</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12" ht="14" x14ac:dyDescent="0.3">
+        <v>4.0010000000000003</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A31" s="3">
         <f t="shared" si="0"/>
         <v>32.555</v>
@@ -2640,13 +4525,13 @@
       <c r="H31" s="3"/>
       <c r="I31" s="3"/>
       <c r="K31" s="3">
-        <v>45</v>
+        <v>2622</v>
       </c>
       <c r="L31" s="3">
-        <v>0.316</v>
-      </c>
-    </row>
-    <row r="32" spans="1:12" ht="14" x14ac:dyDescent="0.3">
+        <v>4.4989999999999997</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A32" s="3">
         <f t="shared" si="0"/>
         <v>129.274</v>
@@ -2665,13 +4550,13 @@
       <c r="I32" s="3"/>
       <c r="J32" s="9"/>
       <c r="K32" s="3">
-        <v>125</v>
+        <v>2945</v>
       </c>
       <c r="L32" s="3">
-        <v>0.44600000000000001</v>
-      </c>
-    </row>
-    <row r="33" spans="1:12" ht="14" x14ac:dyDescent="0.3">
+        <v>4.9969999999999999</v>
+      </c>
+    </row>
+    <row r="33" spans="1:17" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A33" s="3">
         <f t="shared" si="0"/>
         <v>26.571999999999999</v>
@@ -2688,14 +4573,10 @@
       </c>
       <c r="H33" s="3"/>
       <c r="I33" s="3"/>
-      <c r="K33" s="3">
-        <v>199</v>
-      </c>
-      <c r="L33" s="3">
-        <v>0.56299999999999994</v>
-      </c>
-    </row>
-    <row r="34" spans="1:12" ht="14" x14ac:dyDescent="0.3">
+      <c r="K33" s="3"/>
+      <c r="L33" s="3"/>
+    </row>
+    <row r="34" spans="1:17" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A34" s="3">
         <f t="shared" si="0"/>
         <v>104.12</v>
@@ -2712,14 +4593,14 @@
       </c>
       <c r="H34" s="3"/>
       <c r="I34" s="3"/>
-      <c r="K34" s="3">
-        <v>592</v>
-      </c>
-      <c r="L34" s="3">
-        <v>1.1779999999999999</v>
-      </c>
-    </row>
-    <row r="35" spans="1:12" ht="14" x14ac:dyDescent="0.3">
+      <c r="K34" s="3"/>
+      <c r="L34" s="3"/>
+      <c r="P34">
+        <f>5/2950</f>
+        <v>1.6949152542372881E-3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:17" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A35" s="3">
         <f>F29*J29</f>
         <v>0</v>
@@ -2736,14 +4617,10 @@
       </c>
       <c r="H35" s="3"/>
       <c r="I35" s="3"/>
-      <c r="K35" s="3">
-        <v>519</v>
-      </c>
-      <c r="L35" s="3">
-        <v>1.0649999999999999</v>
-      </c>
-    </row>
-    <row r="36" spans="1:12" ht="14" x14ac:dyDescent="0.3">
+      <c r="K35" s="3"/>
+      <c r="L35" s="3"/>
+    </row>
+    <row r="36" spans="1:17" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A36" s="3">
         <f>F30*J30</f>
         <v>0</v>
@@ -2760,14 +4637,10 @@
       </c>
       <c r="H36" s="3"/>
       <c r="I36" s="3"/>
-      <c r="K36" s="3">
-        <v>182</v>
-      </c>
-      <c r="L36" s="3">
-        <v>0.53600000000000003</v>
-      </c>
-    </row>
-    <row r="37" spans="1:12" ht="14" x14ac:dyDescent="0.3">
+      <c r="K36" s="3"/>
+      <c r="L36" s="3"/>
+    </row>
+    <row r="37" spans="1:17" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A37" s="3">
         <f>F31*J31</f>
         <v>0</v>
@@ -2784,14 +4657,10 @@
       </c>
       <c r="H37" s="3"/>
       <c r="I37" s="3"/>
-      <c r="K37" s="3">
-        <v>166</v>
-      </c>
-      <c r="L37" s="3">
-        <v>0.51100000000000001</v>
-      </c>
-    </row>
-    <row r="38" spans="1:12" ht="14" x14ac:dyDescent="0.3">
+      <c r="K37" s="3"/>
+      <c r="L37" s="3"/>
+    </row>
+    <row r="38" spans="1:17" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A38" s="3">
         <f>F32*J32</f>
         <v>0</v>
@@ -2808,14 +4677,10 @@
       </c>
       <c r="H38" s="3"/>
       <c r="I38" s="3"/>
-      <c r="K38" s="3">
-        <v>456</v>
-      </c>
-      <c r="L38" s="3">
-        <v>0.96899999999999997</v>
-      </c>
-    </row>
-    <row r="39" spans="1:12" ht="14" x14ac:dyDescent="0.3">
+      <c r="K38" s="3"/>
+      <c r="L38" s="3"/>
+    </row>
+    <row r="39" spans="1:17" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A39" s="3">
         <f>F33*J33</f>
         <v>0</v>
@@ -2832,104 +4697,247 @@
       </c>
       <c r="H39" s="3"/>
       <c r="I39" s="3"/>
-      <c r="K39" s="3">
-        <v>449</v>
-      </c>
-      <c r="L39" s="3">
-        <v>0.96299999999999997</v>
-      </c>
-    </row>
-    <row r="40" spans="1:12" ht="14" x14ac:dyDescent="0.3">
+      <c r="K39" s="3"/>
+      <c r="L39" s="3"/>
+      <c r="N39" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="O39" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="P39" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q39" s="16" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="40" spans="1:17" ht="14.25" x14ac:dyDescent="0.2">
       <c r="F40" s="3"/>
       <c r="G40" s="3"/>
       <c r="H40" s="3"/>
       <c r="I40" s="3"/>
-      <c r="K40" s="11">
-        <v>195</v>
-      </c>
-      <c r="L40" s="3">
-        <v>0.56200000000000006</v>
-      </c>
-    </row>
-    <row r="41" spans="1:12" ht="14" x14ac:dyDescent="0.3">
+      <c r="K40" s="11"/>
+      <c r="L40" s="3"/>
+      <c r="N40" s="15">
+        <v>0.26800000000000002</v>
+      </c>
+      <c r="O40" s="15">
+        <v>0.252</v>
+      </c>
+      <c r="P40" s="15">
+        <f>O40-N40</f>
+        <v>-1.6000000000000014E-2</v>
+      </c>
+      <c r="Q40" s="17">
+        <f>(P40/N40)*100</f>
+        <v>-5.9701492537313481</v>
+      </c>
+    </row>
+    <row r="41" spans="1:17" ht="14.25" x14ac:dyDescent="0.2">
       <c r="F41" s="3"/>
       <c r="G41" s="3"/>
       <c r="H41" s="3"/>
       <c r="I41" s="3"/>
-      <c r="K41" s="11">
-        <v>582</v>
-      </c>
-      <c r="L41" s="11">
-        <v>1.1719999999999999</v>
-      </c>
-    </row>
-    <row r="42" spans="1:12" ht="14" x14ac:dyDescent="0.3">
+      <c r="K41" s="11"/>
+      <c r="L41" s="11"/>
+      <c r="N41" s="15">
+        <v>0.499</v>
+      </c>
+      <c r="O41" s="15">
+        <v>0.45700000000000002</v>
+      </c>
+      <c r="P41" s="15">
+        <f t="shared" ref="P41:P50" si="2">O41-N41</f>
+        <v>-4.1999999999999982E-2</v>
+      </c>
+      <c r="Q41" s="17">
+        <f t="shared" ref="Q41:Q50" si="3">(P41/N41)*100</f>
+        <v>-8.4168336673346644</v>
+      </c>
+    </row>
+    <row r="42" spans="1:17" ht="14.25" x14ac:dyDescent="0.2">
       <c r="F42" s="3"/>
       <c r="G42" s="3"/>
       <c r="H42" s="3"/>
       <c r="I42" s="3"/>
-      <c r="K42" s="11">
-        <v>237</v>
-      </c>
-      <c r="L42" s="11">
-        <v>0.627</v>
-      </c>
-    </row>
-    <row r="43" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="K43" s="11">
-        <v>785</v>
-      </c>
-      <c r="L43" s="11">
-        <v>1.4910000000000001</v>
-      </c>
-    </row>
-    <row r="44" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="K44" s="11">
-        <v>678</v>
-      </c>
-      <c r="L44" s="11">
-        <v>1.3180000000000001</v>
-      </c>
-    </row>
-    <row r="45" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="K45" s="11">
-        <v>216</v>
-      </c>
-      <c r="L45" s="11">
-        <v>0.59399999999999997</v>
-      </c>
-    </row>
-    <row r="46" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="K46" s="11">
-        <v>380</v>
-      </c>
-      <c r="L46" s="11">
-        <v>0.85099999999999998</v>
-      </c>
-    </row>
-    <row r="47" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="K47" s="11">
-        <v>555</v>
-      </c>
-      <c r="L47" s="11">
-        <v>1.119</v>
-      </c>
-    </row>
-    <row r="48" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="K48" s="11">
-        <v>306</v>
-      </c>
-      <c r="L48" s="11">
-        <v>0.73499999999999999</v>
-      </c>
-    </row>
-    <row r="49" spans="11:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="K49" s="11">
-        <v>359</v>
-      </c>
-      <c r="L49" s="11">
-        <v>0.81899999999999995</v>
-      </c>
+      <c r="K42" s="11"/>
+      <c r="L42" s="11"/>
+      <c r="N42" s="15">
+        <v>1.0029999999999999</v>
+      </c>
+      <c r="O42" s="15">
+        <v>0.95499999999999996</v>
+      </c>
+      <c r="P42" s="15">
+        <f t="shared" si="2"/>
+        <v>-4.7999999999999932E-2</v>
+      </c>
+      <c r="Q42" s="17">
+        <f t="shared" si="3"/>
+        <v>-4.7856430707876303</v>
+      </c>
+    </row>
+    <row r="43" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K43" s="11"/>
+      <c r="L43" s="11"/>
+      <c r="N43" s="15">
+        <v>1.502</v>
+      </c>
+      <c r="O43" s="15">
+        <v>1.456</v>
+      </c>
+      <c r="P43" s="15">
+        <f t="shared" si="2"/>
+        <v>-4.6000000000000041E-2</v>
+      </c>
+      <c r="Q43" s="17">
+        <f t="shared" si="3"/>
+        <v>-3.0625832223701757</v>
+      </c>
+    </row>
+    <row r="44" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K44" s="11"/>
+      <c r="L44" s="11"/>
+      <c r="N44" s="15">
+        <v>1.998</v>
+      </c>
+      <c r="O44" s="15">
+        <v>1.9650000000000001</v>
+      </c>
+      <c r="P44" s="15">
+        <f t="shared" si="2"/>
+        <v>-3.2999999999999918E-2</v>
+      </c>
+      <c r="Q44" s="17">
+        <f t="shared" si="3"/>
+        <v>-1.6516516516516477</v>
+      </c>
+    </row>
+    <row r="45" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K45" s="11"/>
+      <c r="L45" s="11"/>
+      <c r="N45" s="15">
+        <v>2.5</v>
+      </c>
+      <c r="O45" s="15">
+        <v>2.4700000000000002</v>
+      </c>
+      <c r="P45" s="15">
+        <f t="shared" si="2"/>
+        <v>-2.9999999999999805E-2</v>
+      </c>
+      <c r="Q45" s="17">
+        <f t="shared" si="3"/>
+        <v>-1.1999999999999922</v>
+      </c>
+    </row>
+    <row r="46" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K46" s="11"/>
+      <c r="L46" s="11"/>
+      <c r="N46" s="15">
+        <v>2.9990000000000001</v>
+      </c>
+      <c r="O46" s="15">
+        <v>2.9830000000000001</v>
+      </c>
+      <c r="P46" s="15">
+        <f t="shared" si="2"/>
+        <v>-1.6000000000000014E-2</v>
+      </c>
+      <c r="Q46" s="17">
+        <f t="shared" si="3"/>
+        <v>-0.53351117039013052</v>
+      </c>
+    </row>
+    <row r="47" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K47" s="11"/>
+      <c r="L47" s="11"/>
+      <c r="N47" s="15">
+        <v>3.4990000000000001</v>
+      </c>
+      <c r="O47" s="15">
+        <v>3.4870000000000001</v>
+      </c>
+      <c r="P47" s="15">
+        <f t="shared" si="2"/>
+        <v>-1.2000000000000011E-2</v>
+      </c>
+      <c r="Q47" s="17">
+        <f t="shared" si="3"/>
+        <v>-0.34295513003715378</v>
+      </c>
+    </row>
+    <row r="48" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K48" s="11"/>
+      <c r="L48" s="11"/>
+      <c r="N48" s="15">
+        <v>4.0039999999999996</v>
+      </c>
+      <c r="O48" s="15">
+        <v>4.0030000000000001</v>
+      </c>
+      <c r="P48" s="15">
+        <f t="shared" si="2"/>
+        <v>-9.9999999999944578E-4</v>
+      </c>
+      <c r="Q48" s="17">
+        <f t="shared" si="3"/>
+        <v>-2.4975024975011136E-2</v>
+      </c>
+    </row>
+    <row r="49" spans="11:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K49" s="11"/>
+      <c r="L49" s="11"/>
+      <c r="N49" s="15">
+        <v>4.4989999999999997</v>
+      </c>
+      <c r="O49" s="15">
+        <v>4.5110000000000001</v>
+      </c>
+      <c r="P49" s="15">
+        <f t="shared" si="2"/>
+        <v>1.2000000000000455E-2</v>
+      </c>
+      <c r="Q49" s="17">
+        <f t="shared" si="3"/>
+        <v>0.26672593909758735</v>
+      </c>
+    </row>
+    <row r="50" spans="11:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="N50" s="15">
+        <v>4.9969999999999999</v>
+      </c>
+      <c r="O50" s="15">
+        <v>5.0430000000000001</v>
+      </c>
+      <c r="P50" s="15">
+        <f t="shared" si="2"/>
+        <v>4.6000000000000263E-2</v>
+      </c>
+      <c r="Q50" s="17">
+        <f t="shared" si="3"/>
+        <v>0.92055233139884463</v>
+      </c>
+    </row>
+    <row r="51" spans="11:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="N51" s="15"/>
+      <c r="O51" s="15"/>
+      <c r="P51" s="14"/>
+      <c r="Q51" s="17"/>
+    </row>
+    <row r="52" spans="11:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="N52" s="13"/>
+      <c r="O52" s="13"/>
+      <c r="Q52" s="17"/>
+    </row>
+    <row r="53" spans="11:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="N53" s="13"/>
+      <c r="O53" s="13"/>
+    </row>
+    <row r="54" spans="11:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="N54" s="12"/>
+      <c r="O54" s="12"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -2938,8 +4946,8 @@
     <hyperlink ref="D4" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.74805555555555558" right="0.74805555555555558" top="1.3776388888888889" bottom="1.3776388888888889" header="0.98388888888888892" footer="0.98388888888888892"/>
-  <pageSetup paperSize="0" fitToWidth="0" fitToHeight="0" orientation="portrait" horizontalDpi="0" verticalDpi="0" copies="0"/>
+  <pageSetup paperSize="9" fitToWidth="0" fitToHeight="0" orientation="portrait" r:id="rId4"/>
   <headerFooter alignWithMargins="0"/>
-  <drawing r:id="rId4"/>
+  <drawing r:id="rId5"/>
 </worksheet>
 </file>